--- a/data/trans_orig/P2A_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P2A_R-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con alguna condición, enfermedad crónica o limitación en 2007</t>
+          <t>Hogares según si tienen personas con alguna condición, enfermedad crónica o limitación en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>102838</t>
+          <t>102636</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>140306</t>
+          <t>139762</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>165311</t>
+          <t>161724</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>206844</t>
+          <t>203204</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>35,36%</t>
+          <t>34,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>44,25%</t>
+          <t>43,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>275099</t>
+          <t>277386</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>336043</t>
+          <t>332048</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>34,95%</t>
+          <t>34,53%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>353758</t>
+          <t>354302</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>391226</t>
+          <t>391428</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>71,6%</t>
+          <t>71,71%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>79,19%</t>
+          <t>79,23%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>260645</t>
+          <t>264285</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>302178</t>
+          <t>305765</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>55,75%</t>
+          <t>56,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>64,64%</t>
+          <t>65,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>625510</t>
+          <t>629505</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>686454</t>
+          <t>684167</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>65,05%</t>
+          <t>65,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>71,39%</t>
+          <t>71,15%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>201778</t>
+          <t>200812</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>252417</t>
+          <t>252799</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>34,37%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>256185</t>
+          <t>251684</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>304457</t>
+          <t>307976</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>40,96%</t>
+          <t>40,24%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>48,67%</t>
+          <t>49,24%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>471098</t>
+          <t>474040</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>541283</t>
+          <t>544982</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>34,61%</t>
+          <t>34,83%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>39,77%</t>
+          <t>40,04%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>483072</t>
+          <t>482690</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>533711</t>
+          <t>534677</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>65,68%</t>
+          <t>65,63%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>72,57%</t>
+          <t>72,7%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>321037</t>
+          <t>317518</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>369309</t>
+          <t>373810</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>51,33%</t>
+          <t>50,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>59,04%</t>
+          <t>59,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>819699</t>
+          <t>816000</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>889884</t>
+          <t>886942</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>60,23%</t>
+          <t>59,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>65,39%</t>
+          <t>65,17%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>211434</t>
+          <t>210000</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>260125</t>
+          <t>261131</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>33,11%</t>
+          <t>32,88%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>40,73%</t>
+          <t>40,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>359075</t>
+          <t>359726</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>410099</t>
+          <t>410045</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>52,06%</t>
+          <t>52,15%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>59,46%</t>
+          <t>59,45%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>583804</t>
+          <t>582841</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>654105</t>
+          <t>658408</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>43,95%</t>
+          <t>43,88%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>49,24%</t>
+          <t>49,56%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>378543</t>
+          <t>377537</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>427234</t>
+          <t>428668</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>59,27%</t>
+          <t>59,11%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>66,89%</t>
+          <t>67,12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>279645</t>
+          <t>279699</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>330669</t>
+          <t>330018</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>40,54%</t>
+          <t>40,55%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>47,94%</t>
+          <t>47,85%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>674307</t>
+          <t>670004</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>744608</t>
+          <t>745571</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>50,76%</t>
+          <t>50,44%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>56,05%</t>
+          <t>56,12%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>240270</t>
+          <t>240465</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>289506</t>
+          <t>288703</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>46,28%</t>
+          <t>46,32%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>55,77%</t>
+          <t>55,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>323353</t>
+          <t>321970</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>366199</t>
+          <t>363940</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>62,71%</t>
+          <t>62,44%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>71,02%</t>
+          <t>70,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>576605</t>
+          <t>573985</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>641161</t>
+          <t>638035</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>55,72%</t>
+          <t>55,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>61,96%</t>
+          <t>61,66%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>229641</t>
+          <t>230444</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>278877</t>
+          <t>278682</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>44,23%</t>
+          <t>44,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>53,72%</t>
+          <t>53,68%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>149443</t>
+          <t>151702</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>192289</t>
+          <t>193672</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>29,42%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>37,29%</t>
+          <t>37,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>393628</t>
+          <t>396754</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>458184</t>
+          <t>460804</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>38,04%</t>
+          <t>38,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>44,28%</t>
+          <t>44,53%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>280242</t>
+          <t>280760</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>312156</t>
+          <t>313730</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>72,47%</t>
+          <t>72,6%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>80,72%</t>
+          <t>81,13%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>307149</t>
+          <t>308586</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>339117</t>
+          <t>338998</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>76,03%</t>
+          <t>76,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>83,94%</t>
+          <t>83,91%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>595805</t>
+          <t>597277</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>642477</t>
+          <t>642371</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>75,35%</t>
+          <t>75,54%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>81,25%</t>
+          <t>81,24%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>74554</t>
+          <t>72980</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>106468</t>
+          <t>105950</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>27,4%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>64869</t>
+          <t>64988</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>96837</t>
+          <t>95400</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>148219</t>
+          <t>148325</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>194891</t>
+          <t>193419</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>24,46%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>223041</t>
+          <t>222856</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>250035</t>
+          <t>249038</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>76,23%</t>
+          <t>76,17%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>85,46%</t>
+          <t>85,12%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>307329</t>
+          <t>308432</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>326417</t>
+          <t>326890</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>89,62%</t>
+          <t>89,94%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>537937</t>
+          <t>537411</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>570572</t>
+          <t>569981</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>84,65%</t>
+          <t>84,56%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>89,78%</t>
+          <t>89,69%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>42548</t>
+          <t>43545</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>69542</t>
+          <t>69727</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>16517</t>
+          <t>16044</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>35605</t>
+          <t>34502</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>64945</t>
+          <t>65536</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>97580</t>
+          <t>98106</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,44%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>186644</t>
+          <t>186186</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>201387</t>
+          <t>201800</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>88,93%</t>
+          <t>88,71%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>310404</t>
+          <t>310479</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>326708</t>
+          <t>326332</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>503545</t>
+          <t>501991</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>524851</t>
+          <t>524118</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,31%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,38%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>8496</t>
+          <t>8083</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>23239</t>
+          <t>23697</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>7200</t>
+          <t>7576</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>23504</t>
+          <t>23429</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>18940</t>
+          <t>19673</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>40246</t>
+          <t>41800</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,69%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1519872</t>
+          <t>1520616</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1638673</t>
+          <t>1636835</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>46,39%</t>
+          <t>46,41%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>50,01%</t>
+          <t>49,96%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2100896</t>
+          <t>2105314</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2222608</t>
+          <t>2214989</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>62,17%</t>
+          <t>62,3%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>65,77%</t>
+          <t>65,55%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3652324</t>
+          <t>3655098</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3821214</t>
+          <t>3821684</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>54,87%</t>
+          <t>54,92%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>57,41%</t>
+          <t>57,42%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1637870</t>
+          <t>1639708</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1756671</t>
+          <t>1755927</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>49,99%</t>
+          <t>50,04%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>53,61%</t>
+          <t>53,59%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1156589</t>
+          <t>1164208</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1278301</t>
+          <t>1273883</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>34,23%</t>
+          <t>34,45%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>37,83%</t>
+          <t>37,7%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2834527</t>
+          <t>2834057</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3003417</t>
+          <t>3000643</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>42,59%</t>
+          <t>42,58%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>45,13%</t>
+          <t>45,08%</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con alguna condición, enfermedad crónica o limitación en 2012</t>
+          <t>Hogares según si tienen personas con alguna condición, enfermedad crónica o limitación en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>133108</t>
+          <t>131676</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>172570</t>
+          <t>173771</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>28,99%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>38,0%</t>
+          <t>38,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>170228</t>
+          <t>169248</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>211365</t>
+          <t>211115</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>39,57%</t>
+          <t>39,34%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>49,13%</t>
+          <t>49,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>313648</t>
+          <t>312413</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>370648</t>
+          <t>371133</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>35,47%</t>
+          <t>35,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>41,91%</t>
+          <t>41,97%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>281576</t>
+          <t>280375</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>321038</t>
+          <t>322470</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>62,0%</t>
+          <t>61,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>70,69%</t>
+          <t>71,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>218865</t>
+          <t>219115</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>260002</t>
+          <t>260982</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>50,87%</t>
+          <t>50,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>60,43%</t>
+          <t>60,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>513728</t>
+          <t>513243</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>570728</t>
+          <t>571963</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>58,09%</t>
+          <t>58,03%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>64,53%</t>
+          <t>64,67%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>251483</t>
+          <t>253601</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>303318</t>
+          <t>307473</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>36,6%</t>
+          <t>36,91%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>44,15%</t>
+          <t>44,75%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>275132</t>
+          <t>277479</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>328657</t>
+          <t>328487</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>45,08%</t>
+          <t>45,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>53,86%</t>
+          <t>53,83%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>545053</t>
+          <t>547024</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>619537</t>
+          <t>619394</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>42,01%</t>
+          <t>42,16%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>47,75%</t>
+          <t>47,74%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>383769</t>
+          <t>379614</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>435604</t>
+          <t>433486</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>55,85%</t>
+          <t>55,25%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>63,4%</t>
+          <t>63,09%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>281598</t>
+          <t>281768</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>335123</t>
+          <t>332776</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>46,14%</t>
+          <t>46,17%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>54,92%</t>
+          <t>54,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>677805</t>
+          <t>677948</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>752289</t>
+          <t>750318</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>52,25%</t>
+          <t>52,26%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>57,99%</t>
+          <t>57,84%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>263591</t>
+          <t>265647</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>316814</t>
+          <t>319188</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>38,66%</t>
+          <t>38,96%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>46,46%</t>
+          <t>46,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>386596</t>
+          <t>386292</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>441451</t>
+          <t>443218</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>54,39%</t>
+          <t>54,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>62,1%</t>
+          <t>62,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>664363</t>
+          <t>667174</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>744334</t>
+          <t>744638</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>47,7%</t>
+          <t>47,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>53,44%</t>
+          <t>53,47%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>365049</t>
+          <t>362675</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>418272</t>
+          <t>416216</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>53,54%</t>
+          <t>53,19%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>61,34%</t>
+          <t>61,04%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>269399</t>
+          <t>267632</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>324254</t>
+          <t>324558</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>37,9%</t>
+          <t>37,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>45,61%</t>
+          <t>45,66%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>648378</t>
+          <t>648074</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>728349</t>
+          <t>725538</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>46,56%</t>
+          <t>46,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>52,3%</t>
+          <t>52,1%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>293245</t>
+          <t>291982</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>345630</t>
+          <t>344542</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>47,71%</t>
+          <t>47,51%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>56,24%</t>
+          <t>56,06%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>430275</t>
+          <t>427790</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>474393</t>
+          <t>475250</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>69,83%</t>
+          <t>69,42%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>76,99%</t>
+          <t>77,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>732252</t>
+          <t>737953</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>808926</t>
+          <t>809741</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>59,49%</t>
+          <t>59,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>65,72%</t>
+          <t>65,79%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>268987</t>
+          <t>270075</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>321372</t>
+          <t>322635</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>43,76%</t>
+          <t>43,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>52,29%</t>
+          <t>52,49%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>141806</t>
+          <t>140949</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>185924</t>
+          <t>188409</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>30,58%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>421890</t>
+          <t>421075</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>498564</t>
+          <t>492863</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>34,28%</t>
+          <t>34,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>40,51%</t>
+          <t>40,04%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>314930</t>
+          <t>314390</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>350034</t>
+          <t>349609</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>73,34%</t>
+          <t>73,21%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>81,51%</t>
+          <t>81,41%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>378147</t>
+          <t>377263</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>407101</t>
+          <t>405913</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>84,45%</t>
+          <t>84,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>90,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>702264</t>
+          <t>702776</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>749988</t>
+          <t>749406</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>80,05%</t>
+          <t>80,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>85,5%</t>
+          <t>85,43%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>79395</t>
+          <t>79820</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>114499</t>
+          <t>115039</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>40699</t>
+          <t>41887</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>69653</t>
+          <t>70537</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>127241</t>
+          <t>127823</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>174965</t>
+          <t>174453</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>19,89%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>281630</t>
+          <t>280453</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>298939</t>
+          <t>298815</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>90,53%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>323591</t>
+          <t>323440</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>341810</t>
+          <t>342125</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>91,37%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>612387</t>
+          <t>609912</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>637608</t>
+          <t>636922</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>91,88%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>95,95%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>10847</t>
+          <t>10971</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>28156</t>
+          <t>29333</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>12186</t>
+          <t>11871</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>30405</t>
+          <t>30556</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>26174</t>
+          <t>26860</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>51395</t>
+          <t>53870</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>8,12%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>229931</t>
+          <t>228793</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>243521</t>
+          <t>243440</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>91,57%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>370801</t>
+          <t>370611</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>384390</t>
+          <t>384354</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>605604</t>
+          <t>604784</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>624702</t>
+          <t>624461</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,75%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>6330</t>
+          <t>6411</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>19920</t>
+          <t>21058</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>4589</t>
+          <t>4625</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>18178</t>
+          <t>18368</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>14128</t>
+          <t>14369</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>33226</t>
+          <t>34046</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,33%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1849476</t>
+          <t>1850019</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1968067</t>
+          <t>1965044</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>53,97%</t>
+          <t>53,99%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>57,43%</t>
+          <t>57,34%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2403543</t>
+          <t>2409124</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2519341</t>
+          <t>2519358</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,7 +6163,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>67,55%</t>
+          <t>67,7%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4285196</t>
+          <t>4292739</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4452118</t>
+          <t>4457638</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>61,35%</t>
+          <t>61,46%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>63,74%</t>
+          <t>63,82%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1458712</t>
+          <t>1461735</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1577303</t>
+          <t>1576760</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>42,57%</t>
+          <t>42,66%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>46,03%</t>
+          <t>46,01%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1038968</t>
+          <t>1038951</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1154766</t>
+          <t>1149185</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6281,7 +6281,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>32,45%</t>
+          <t>32,3%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2532970</t>
+          <t>2527450</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2699892</t>
+          <t>2692349</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>36,26%</t>
+          <t>36,18%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>38,65%</t>
+          <t>38,54%</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con alguna condición, enfermedad crónica o limitación en 2016</t>
+          <t>Hogares según si tienen personas con alguna condición, enfermedad crónica o limitación en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>115383</t>
+          <t>118665</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>157707</t>
+          <t>159125</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>37,6%</t>
+          <t>37,94%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>128237</t>
+          <t>127239</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>163304</t>
+          <t>164726</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>32,4%</t>
+          <t>32,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>41,26%</t>
+          <t>41,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>253359</t>
+          <t>255241</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>308772</t>
+          <t>309145</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>31,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>37,88%</t>
+          <t>37,92%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>261756</t>
+          <t>260338</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>304080</t>
+          <t>300798</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>62,4%</t>
+          <t>62,06%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>72,49%</t>
+          <t>71,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>232451</t>
+          <t>231029</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>267518</t>
+          <t>268516</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>58,74%</t>
+          <t>58,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>67,6%</t>
+          <t>67,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>506446</t>
+          <t>506073</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>561859</t>
+          <t>559977</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>62,12%</t>
+          <t>62,08%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>68,92%</t>
+          <t>68,69%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>157914</t>
+          <t>155028</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>204548</t>
+          <t>201115</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>26,25%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,64%</t>
+          <t>34,06%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>212259</t>
+          <t>214339</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>259110</t>
+          <t>261046</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>37,66%</t>
+          <t>38,03%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>45,98%</t>
+          <t>46,32%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>379991</t>
+          <t>379943</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>446376</t>
+          <t>445076</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>32,92%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>38,68%</t>
+          <t>38,57%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>385948</t>
+          <t>389381</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>432582</t>
+          <t>435468</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>65,36%</t>
+          <t>65,94%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>73,26%</t>
+          <t>73,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>304434</t>
+          <t>302498</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>351285</t>
+          <t>349205</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>54,02%</t>
+          <t>53,68%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>62,34%</t>
+          <t>61,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>707664</t>
+          <t>708964</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>774049</t>
+          <t>774097</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>61,32%</t>
+          <t>61,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>67,07%</t>
+          <t>67,08%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>220189</t>
+          <t>220995</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>269596</t>
+          <t>270743</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>32,91%</t>
+          <t>33,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>40,29%</t>
+          <t>40,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>307410</t>
+          <t>308319</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>356601</t>
+          <t>358037</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>46,48%</t>
+          <t>46,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>53,92%</t>
+          <t>54,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>537636</t>
+          <t>538570</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>614826</t>
+          <t>613279</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>40,41%</t>
+          <t>40,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>46,21%</t>
+          <t>46,09%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>399501</t>
+          <t>398354</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>448908</t>
+          <t>448102</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>59,71%</t>
+          <t>59,54%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>67,09%</t>
+          <t>66,97%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>304785</t>
+          <t>303349</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>353976</t>
+          <t>353067</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>46,08%</t>
+          <t>45,87%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>53,52%</t>
+          <t>53,38%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>715657</t>
+          <t>717204</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>792847</t>
+          <t>791913</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>53,79%</t>
+          <t>53,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>59,59%</t>
+          <t>59,52%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>331420</t>
+          <t>328173</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>384619</t>
+          <t>382048</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>51,3%</t>
+          <t>50,8%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>59,53%</t>
+          <t>59,14%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>377078</t>
+          <t>376058</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>427388</t>
+          <t>427592</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>58,09%</t>
+          <t>57,94%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>65,85%</t>
+          <t>65,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>724322</t>
+          <t>720727</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>795924</t>
+          <t>792782</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>55,93%</t>
+          <t>55,65%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>61,46%</t>
+          <t>61,21%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>261429</t>
+          <t>264000</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>314628</t>
+          <t>317875</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>40,47%</t>
+          <t>40,86%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>48,7%</t>
+          <t>49,2%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>221689</t>
+          <t>221485</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>271999</t>
+          <t>273019</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>34,15%</t>
+          <t>34,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>41,91%</t>
+          <t>42,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>499201</t>
+          <t>502343</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>570803</t>
+          <t>574398</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>38,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>44,07%</t>
+          <t>44,35%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>297855</t>
+          <t>296152</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>342210</t>
+          <t>341565</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>62,32%</t>
+          <t>61,97%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>71,6%</t>
+          <t>71,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>391522</t>
+          <t>392598</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>430215</t>
+          <t>428656</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>78,8%</t>
+          <t>79,02%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>86,59%</t>
+          <t>86,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>701916</t>
+          <t>702578</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>759400</t>
+          <t>761040</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>72,01%</t>
+          <t>72,08%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>77,91%</t>
+          <t>78,07%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>135708</t>
+          <t>136353</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>180063</t>
+          <t>181766</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>28,53%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>37,68%</t>
+          <t>38,03%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>66634</t>
+          <t>68193</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>105327</t>
+          <t>104251</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>215367</t>
+          <t>213727</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>272851</t>
+          <t>272189</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>21,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>27,92%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>285028</t>
+          <t>283739</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>308694</t>
+          <t>307424</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>85,25%</t>
+          <t>84,87%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>91,95%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>332137</t>
+          <t>332340</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>356119</t>
+          <t>354968</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>87,92%</t>
+          <t>87,98%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>623634</t>
+          <t>624066</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>656923</t>
+          <t>657327</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>87,58%</t>
+          <t>87,64%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>92,31%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>25636</t>
+          <t>26906</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>49302</t>
+          <t>50591</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>21643</t>
+          <t>22794</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>45625</t>
+          <t>45422</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>55169</t>
+          <t>54765</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>88458</t>
+          <t>88026</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,36%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>231208</t>
+          <t>232261</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>246955</t>
+          <t>246847</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>90,37%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>378317</t>
+          <t>377794</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>393901</t>
+          <t>393809</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>615909</t>
+          <t>615331</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>637079</t>
+          <t>637126</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,95%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>10043</t>
+          <t>10151</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>25790</t>
+          <t>24737</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>6268</t>
+          <t>6360</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>21852</t>
+          <t>22375</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>20088</t>
+          <t>20041</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>41258</t>
+          <t>41836</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,37%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1712701</t>
+          <t>1714718</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1832928</t>
+          <t>1829476</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>50,46%</t>
+          <t>50,52%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>54,0%</t>
+          <t>53,9%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2202021</t>
+          <t>2204921</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2314803</t>
+          <t>2318325</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>62,12%</t>
+          <t>62,21%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>65,31%</t>
+          <t>65,41%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3949120</t>
+          <t>3954961</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4116959</t>
+          <t>4114052</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>56,91%</t>
+          <t>57,0%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>59,33%</t>
+          <t>59,29%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1561422</t>
+          <t>1564874</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1681649</t>
+          <t>1679632</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>46,0%</t>
+          <t>46,1%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>49,54%</t>
+          <t>49,48%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1229739</t>
+          <t>1226217</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1342521</t>
+          <t>1339621</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>34,69%</t>
+          <t>34,59%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>37,88%</t>
+          <t>37,79%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2821933</t>
+          <t>2824840</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2989772</t>
+          <t>2983931</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>40,67%</t>
+          <t>40,71%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>43,09%</t>
+          <t>43,0%</t>
         </is>
       </c>
     </row>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con alguna condición, enfermedad crónica o limitación en 2023</t>
+          <t>Hogares según si tienen personas con alguna condición, enfermedad crónica o limitación en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9670,12 +9670,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>85274</t>
+          <t>84062</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>149996</t>
+          <t>149159</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>37,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>67357</t>
+          <t>66973</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>111716</t>
+          <t>111138</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>35,67%</t>
+          <t>35,48%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9740,12 +9740,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>166270</t>
+          <t>165126</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>248037</t>
+          <t>244639</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>34,78%</t>
+          <t>34,3%</t>
         </is>
       </c>
     </row>
@@ -9783,12 +9783,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>249991</t>
+          <t>250828</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>314713</t>
+          <t>315925</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9798,12 +9798,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>62,5%</t>
+          <t>62,71%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>78,68%</t>
+          <t>78,98%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9818,12 +9818,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>201484</t>
+          <t>202062</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>245843</t>
+          <t>246227</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9833,12 +9833,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>64,33%</t>
+          <t>64,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>78,49%</t>
+          <t>78,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9853,12 +9853,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>465150</t>
+          <t>468548</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>546917</t>
+          <t>548061</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>65,22%</t>
+          <t>65,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>76,69%</t>
+          <t>76,85%</t>
         </is>
       </c>
     </row>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>96882</t>
+          <t>99239</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>147829</t>
+          <t>146118</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,9%</t>
+          <t>34,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>77256</t>
+          <t>79495</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>153002</t>
+          <t>155836</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>30,43%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10083,12 +10083,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>184399</t>
+          <t>188016</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>283529</t>
+          <t>284718</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>30,43%</t>
         </is>
       </c>
     </row>
@@ -10126,12 +10126,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>275718</t>
+          <t>277429</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>326665</t>
+          <t>324308</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>65,1%</t>
+          <t>65,5%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>77,13%</t>
+          <t>76,57%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>359091</t>
+          <t>356257</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>434837</t>
+          <t>432598</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>70,12%</t>
+          <t>69,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,91%</t>
+          <t>84,48%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10196,12 +10196,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>652111</t>
+          <t>650922</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>751241</t>
+          <t>747624</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>69,7%</t>
+          <t>69,57%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,29%</t>
+          <t>79,91%</t>
         </is>
       </c>
     </row>
@@ -10356,12 +10356,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>111711</t>
+          <t>116543</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>154776</t>
+          <t>157272</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>138085</t>
+          <t>129923</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>197884</t>
+          <t>199968</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>33,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>260517</t>
+          <t>261730</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>338033</t>
+          <t>338470</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10441,12 +10441,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>30,0%</t>
         </is>
       </c>
     </row>
@@ -10469,12 +10469,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>381562</t>
+          <t>379066</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>424627</t>
+          <t>419795</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>71,14%</t>
+          <t>70,68%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>79,17%</t>
+          <t>78,27%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>394118</t>
+          <t>392034</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>453917</t>
+          <t>462079</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>66,57%</t>
+          <t>66,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>76,67%</t>
+          <t>78,05%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10539,12 +10539,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>790307</t>
+          <t>789870</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>867823</t>
+          <t>866610</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>70,04%</t>
+          <t>70,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>76,91%</t>
+          <t>76,8%</t>
         </is>
       </c>
     </row>
@@ -10699,12 +10699,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>109359</t>
+          <t>108373</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>356138</t>
+          <t>354972</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>40,12%</t>
+          <t>39,98%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>251874</t>
+          <t>247699</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>322842</t>
+          <t>322565</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10749,12 +10749,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>35,33%</t>
+          <t>34,75%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>45,29%</t>
+          <t>45,25%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10769,12 +10769,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>309109</t>
+          <t>348805</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>658388</t>
+          <t>662693</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10784,12 +10784,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>41,13%</t>
+          <t>41,4%</t>
         </is>
       </c>
     </row>
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>531648</t>
+          <t>532814</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>778427</t>
+          <t>779413</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>59,88%</t>
+          <t>60,02%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,68%</t>
+          <t>87,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10847,12 +10847,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>390039</t>
+          <t>390316</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>461007</t>
+          <t>465182</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10862,12 +10862,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>54,71%</t>
+          <t>54,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>64,67%</t>
+          <t>65,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>942279</t>
+          <t>937974</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1291558</t>
+          <t>1251862</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10897,12 +10897,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>58,87%</t>
+          <t>58,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>80,69%</t>
+          <t>78,21%</t>
         </is>
       </c>
     </row>
@@ -11042,12 +11042,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>275695</t>
+          <t>274241</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>319587</t>
+          <t>319166</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>49,12%</t>
+          <t>48,86%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>56,94%</t>
+          <t>56,87%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>282777</t>
+          <t>283458</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>317537</t>
+          <t>319988</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>51,61%</t>
+          <t>51,73%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>57,95%</t>
+          <t>58,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11112,12 +11112,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>569116</t>
+          <t>570430</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>624616</t>
+          <t>625548</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11127,12 +11127,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>51,31%</t>
+          <t>51,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>56,32%</t>
+          <t>56,4%</t>
         </is>
       </c>
     </row>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>241647</t>
+          <t>242068</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>285539</t>
+          <t>286993</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11170,12 +11170,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>43,06%</t>
+          <t>43,13%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>50,88%</t>
+          <t>51,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11190,12 +11190,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>230368</t>
+          <t>227917</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>265128</t>
+          <t>264447</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11205,12 +11205,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>42,05%</t>
+          <t>41,6%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>48,39%</t>
+          <t>48,27%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11225,12 +11225,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>484523</t>
+          <t>483591</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>540023</t>
+          <t>538709</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11240,12 +11240,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>43,68%</t>
+          <t>43,6%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>48,69%</t>
+          <t>48,57%</t>
         </is>
       </c>
     </row>
@@ -11385,12 +11385,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>184305</t>
+          <t>185915</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>214125</t>
+          <t>216279</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>50,06%</t>
+          <t>50,5%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>58,16%</t>
+          <t>58,75%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>391568</t>
+          <t>392704</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>548461</t>
+          <t>545258</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>64,36%</t>
+          <t>64,55%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>89,63%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11455,12 +11455,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>580850</t>
+          <t>579561</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>808391</t>
+          <t>815314</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11470,12 +11470,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>59,48%</t>
+          <t>59,35%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>82,78%</t>
+          <t>83,49%</t>
         </is>
       </c>
     </row>
@@ -11498,12 +11498,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>154040</t>
+          <t>151886</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>183860</t>
+          <t>182250</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>41,84%</t>
+          <t>41,25%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>49,94%</t>
+          <t>49,5%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>59907</t>
+          <t>63110</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>216800</t>
+          <t>215664</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>35,64%</t>
+          <t>35,45%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11568,12 +11568,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>168142</t>
+          <t>161219</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>395683</t>
+          <t>396972</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11583,12 +11583,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>40,52%</t>
+          <t>40,65%</t>
         </is>
       </c>
     </row>
@@ -11728,12 +11728,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>191958</t>
+          <t>191394</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>215657</t>
+          <t>214947</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>67,89%</t>
+          <t>67,69%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>76,27%</t>
+          <t>76,02%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>312901</t>
+          <t>312495</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>339641</t>
+          <t>337242</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>73,48%</t>
+          <t>73,38%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>79,76%</t>
+          <t>79,2%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11798,12 +11798,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>511923</t>
+          <t>511715</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>548887</t>
+          <t>545290</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11813,12 +11813,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>72,25%</t>
+          <t>72,22%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>77,46%</t>
+          <t>76,95%</t>
         </is>
       </c>
     </row>
@@ -11841,12 +11841,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>67102</t>
+          <t>67812</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>90801</t>
+          <t>91365</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>23,98%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>32,11%</t>
+          <t>32,31%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>86190</t>
+          <t>88589</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>112930</t>
+          <t>113336</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11911,12 +11911,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>159703</t>
+          <t>163300</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>196667</t>
+          <t>196875</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11926,12 +11926,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>27,78%</t>
         </is>
       </c>
     </row>
@@ -12071,12 +12071,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1045718</t>
+          <t>1022275</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1448031</t>
+          <t>1443659</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>41,85%</t>
+          <t>41,73%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1639887</t>
+          <t>1633608</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2155738</t>
+          <t>2158123</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>44,17%</t>
+          <t>44,01%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>58,07%</t>
+          <t>58,13%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2816485</t>
+          <t>2822782</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3464703</t>
+          <t>3424282</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>39,27%</t>
+          <t>39,36%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>48,31%</t>
+          <t>47,74%</t>
         </is>
       </c>
     </row>
@@ -12184,12 +12184,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2011786</t>
+          <t>2016158</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2414099</t>
+          <t>2437542</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>58,15%</t>
+          <t>58,27%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>69,78%</t>
+          <t>70,45%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1556542</t>
+          <t>1554157</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2072393</t>
+          <t>2078672</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>41,93%</t>
+          <t>41,87%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>55,83%</t>
+          <t>55,99%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3707394</t>
+          <t>3747815</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4355612</t>
+          <t>4349315</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12269,12 +12269,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>51,69%</t>
+          <t>52,26%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>60,73%</t>
+          <t>60,64%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P2A_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P2A_R-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>102636</t>
+          <t>103589</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>139762</t>
+          <t>140569</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>161724</t>
+          <t>162466</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>203204</t>
+          <t>205475</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>34,59%</t>
+          <t>34,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>43,47%</t>
+          <t>43,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>277386</t>
+          <t>279461</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>332048</t>
+          <t>331610</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>34,53%</t>
+          <t>34,49%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>354302</t>
+          <t>353495</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>391428</t>
+          <t>390475</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>71,71%</t>
+          <t>71,55%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>79,23%</t>
+          <t>79,03%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>264285</t>
+          <t>262014</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>305765</t>
+          <t>305023</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>56,53%</t>
+          <t>56,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>65,41%</t>
+          <t>65,25%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>629505</t>
+          <t>629943</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>684167</t>
+          <t>682092</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>65,47%</t>
+          <t>65,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>71,15%</t>
+          <t>70,94%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>200812</t>
+          <t>205763</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>252799</t>
+          <t>254083</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,37%</t>
+          <t>34,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>251684</t>
+          <t>253257</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>307976</t>
+          <t>305722</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>40,24%</t>
+          <t>40,49%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>49,24%</t>
+          <t>48,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>474040</t>
+          <t>476312</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>544982</t>
+          <t>545253</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>34,83%</t>
+          <t>35,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>40,04%</t>
+          <t>40,06%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>482690</t>
+          <t>481406</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>534677</t>
+          <t>529726</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>65,63%</t>
+          <t>65,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>72,7%</t>
+          <t>72,02%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>317518</t>
+          <t>319772</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>373810</t>
+          <t>372237</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>50,76%</t>
+          <t>51,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>59,76%</t>
+          <t>59,51%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>816000</t>
+          <t>815729</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>886942</t>
+          <t>884670</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>59,96%</t>
+          <t>59,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>65,17%</t>
+          <t>65,0%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>210000</t>
+          <t>209708</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>261131</t>
+          <t>262126</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>32,88%</t>
+          <t>32,84%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>40,89%</t>
+          <t>41,04%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>359726</t>
+          <t>360406</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>410045</t>
+          <t>412263</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>52,15%</t>
+          <t>52,25%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>59,45%</t>
+          <t>59,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>582841</t>
+          <t>580708</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>658408</t>
+          <t>660939</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>43,88%</t>
+          <t>43,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>49,56%</t>
+          <t>49,75%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>377537</t>
+          <t>376542</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>428668</t>
+          <t>428960</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>59,11%</t>
+          <t>58,96%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>67,12%</t>
+          <t>67,16%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>279699</t>
+          <t>277481</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>330018</t>
+          <t>329338</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>40,55%</t>
+          <t>40,23%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>47,85%</t>
+          <t>47,75%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>670004</t>
+          <t>667473</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>745571</t>
+          <t>747704</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>50,44%</t>
+          <t>50,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>56,12%</t>
+          <t>56,29%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>240465</t>
+          <t>240544</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>288703</t>
+          <t>287527</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>46,32%</t>
+          <t>46,33%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>55,61%</t>
+          <t>55,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>321970</t>
+          <t>324172</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>363940</t>
+          <t>365643</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>62,44%</t>
+          <t>62,87%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>70,58%</t>
+          <t>70,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>573985</t>
+          <t>574270</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>638035</t>
+          <t>640427</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>55,47%</t>
+          <t>55,5%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>61,66%</t>
+          <t>61,89%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>230444</t>
+          <t>231620</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>278682</t>
+          <t>278603</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>44,39%</t>
+          <t>44,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>53,68%</t>
+          <t>53,67%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>151702</t>
+          <t>149999</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>193672</t>
+          <t>191470</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>29,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>37,56%</t>
+          <t>37,13%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>396754</t>
+          <t>394362</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>460804</t>
+          <t>460519</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>38,34%</t>
+          <t>38,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>44,53%</t>
+          <t>44,5%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>280760</t>
+          <t>280448</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>313730</t>
+          <t>312809</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>72,6%</t>
+          <t>72,52%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>81,13%</t>
+          <t>80,89%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>308586</t>
+          <t>307507</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>338998</t>
+          <t>338617</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>76,39%</t>
+          <t>76,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>83,91%</t>
+          <t>83,82%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>597277</t>
+          <t>595018</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>642371</t>
+          <t>642705</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>75,54%</t>
+          <t>75,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>81,24%</t>
+          <t>81,28%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>72980</t>
+          <t>73901</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>105950</t>
+          <t>106262</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>27,48%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>64988</t>
+          <t>65369</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>95400</t>
+          <t>96479</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>148325</t>
+          <t>147991</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>193419</t>
+          <t>195678</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>24,75%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>222856</t>
+          <t>221924</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>249038</t>
+          <t>249199</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>76,17%</t>
+          <t>75,85%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>85,12%</t>
+          <t>85,17%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>308432</t>
+          <t>308106</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>326890</t>
+          <t>326410</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>89,94%</t>
+          <t>89,84%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>537411</t>
+          <t>537939</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>569981</t>
+          <t>570571</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>84,56%</t>
+          <t>84,65%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
+          <t>89,78%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>43545</t>
+          <t>43384</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>69727</t>
+          <t>70659</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>16044</t>
+          <t>16524</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>34502</t>
+          <t>34828</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>65536</t>
+          <t>64946</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>98106</t>
+          <t>97578</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,35%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>186186</t>
+          <t>185940</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>201800</t>
+          <t>201391</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>88,71%</t>
+          <t>88,59%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>310479</t>
+          <t>310298</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>326332</t>
+          <t>326006</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>501991</t>
+          <t>502494</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>524118</t>
+          <t>524339</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,42%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>8083</t>
+          <t>8492</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>23697</t>
+          <t>23943</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>7576</t>
+          <t>7902</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>23429</t>
+          <t>23610</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>19673</t>
+          <t>19452</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>41800</t>
+          <t>41297</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,59%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1520616</t>
+          <t>1523547</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1636835</t>
+          <t>1639290</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>46,41%</t>
+          <t>46,5%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>49,96%</t>
+          <t>50,03%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2105314</t>
+          <t>2098769</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2214989</t>
+          <t>2211245</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>62,3%</t>
+          <t>62,11%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>65,55%</t>
+          <t>65,44%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3655098</t>
+          <t>3649928</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3821684</t>
+          <t>3815091</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>54,92%</t>
+          <t>54,84%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>57,42%</t>
+          <t>57,32%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1639708</t>
+          <t>1637253</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1755927</t>
+          <t>1752996</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>50,04%</t>
+          <t>49,97%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>53,59%</t>
+          <t>53,5%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1164208</t>
+          <t>1167952</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1273883</t>
+          <t>1280428</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>34,45%</t>
+          <t>34,56%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>37,7%</t>
+          <t>37,89%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2834057</t>
+          <t>2840650</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3000643</t>
+          <t>3005813</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>42,58%</t>
+          <t>42,68%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>45,08%</t>
+          <t>45,16%</t>
         </is>
       </c>
     </row>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>131676</t>
+          <t>132627</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>173771</t>
+          <t>171806</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>38,26%</t>
+          <t>37,83%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>169248</t>
+          <t>168791</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>211115</t>
+          <t>208953</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>39,34%</t>
+          <t>39,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>49,07%</t>
+          <t>48,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>312413</t>
+          <t>312441</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>371133</t>
+          <t>369049</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3802,7 +3802,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>41,97%</t>
+          <t>41,73%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>280375</t>
+          <t>282340</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>322470</t>
+          <t>321519</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>61,74%</t>
+          <t>62,17%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>71,01%</t>
+          <t>70,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>219115</t>
+          <t>221277</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>260982</t>
+          <t>261439</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>50,93%</t>
+          <t>51,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>60,66%</t>
+          <t>60,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>513243</t>
+          <t>515327</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>571963</t>
+          <t>571935</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>58,03%</t>
+          <t>58,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>253601</t>
+          <t>253201</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>307473</t>
+          <t>305639</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>36,91%</t>
+          <t>36,85%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>44,75%</t>
+          <t>44,48%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>277479</t>
+          <t>276804</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>328487</t>
+          <t>327419</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>45,47%</t>
+          <t>45,36%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>53,83%</t>
+          <t>53,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>547024</t>
+          <t>542411</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>619394</t>
+          <t>614436</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>42,16%</t>
+          <t>41,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>47,74%</t>
+          <t>47,36%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>379614</t>
+          <t>381448</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>433486</t>
+          <t>433886</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>55,25%</t>
+          <t>55,52%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>63,09%</t>
+          <t>63,15%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>281768</t>
+          <t>282836</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>332776</t>
+          <t>333451</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>46,17%</t>
+          <t>46,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>54,53%</t>
+          <t>54,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>677948</t>
+          <t>682906</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>750318</t>
+          <t>754931</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>52,26%</t>
+          <t>52,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>57,84%</t>
+          <t>58,19%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>265647</t>
+          <t>266181</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>319188</t>
+          <t>319372</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>38,96%</t>
+          <t>39,04%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>46,81%</t>
+          <t>46,84%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>386292</t>
+          <t>386034</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>443218</t>
+          <t>439498</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>54,34%</t>
+          <t>54,31%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>62,35%</t>
+          <t>61,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>667174</t>
+          <t>668172</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>744638</t>
+          <t>744453</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>47,9%</t>
+          <t>47,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>53,47%</t>
+          <t>53,45%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>362675</t>
+          <t>362491</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>416216</t>
+          <t>415682</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>53,19%</t>
+          <t>53,16%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>61,04%</t>
+          <t>60,96%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>267632</t>
+          <t>271352</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>324558</t>
+          <t>324816</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>37,65%</t>
+          <t>38,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>45,66%</t>
+          <t>45,69%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>648074</t>
+          <t>648259</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>725538</t>
+          <t>724540</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>46,53%</t>
+          <t>46,55%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>52,1%</t>
+          <t>52,02%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>291982</t>
+          <t>293009</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>344542</t>
+          <t>344612</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>47,51%</t>
+          <t>47,67%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>56,06%</t>
+          <t>56,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>427790</t>
+          <t>428341</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>475250</t>
+          <t>474815</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>69,42%</t>
+          <t>69,51%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>77,13%</t>
+          <t>77,06%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>737953</t>
+          <t>736953</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>809741</t>
+          <t>807201</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>59,96%</t>
+          <t>59,88%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>65,79%</t>
+          <t>65,58%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>270075</t>
+          <t>270005</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>322635</t>
+          <t>321608</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>43,94%</t>
+          <t>43,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>52,49%</t>
+          <t>52,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>140949</t>
+          <t>141384</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>188409</t>
+          <t>187858</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>30,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>421075</t>
+          <t>423615</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>492863</t>
+          <t>493863</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>34,21%</t>
+          <t>34,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>40,04%</t>
+          <t>40,12%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>314390</t>
+          <t>314828</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>349609</t>
+          <t>349484</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>73,21%</t>
+          <t>73,31%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>81,41%</t>
+          <t>81,38%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>377263</t>
+          <t>377467</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>405913</t>
+          <t>406456</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>84,25%</t>
+          <t>84,29%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>90,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>702776</t>
+          <t>699058</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>749406</t>
+          <t>746556</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>80,11%</t>
+          <t>79,69%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>85,43%</t>
+          <t>85,1%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>79820</t>
+          <t>79945</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>115039</t>
+          <t>114601</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>26,79%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>41887</t>
+          <t>41344</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>70537</t>
+          <t>70333</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>127823</t>
+          <t>130673</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>174453</t>
+          <t>178171</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>20,31%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>280453</t>
+          <t>281198</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>298815</t>
+          <t>298813</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,7 +5442,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>90,77%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>323440</t>
+          <t>324898</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>342125</t>
+          <t>342871</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>91,37%</t>
+          <t>91,78%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>609912</t>
+          <t>612891</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>636922</t>
+          <t>637286</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>92,33%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>96,01%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>10971</t>
+          <t>10973</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>29333</t>
+          <t>28588</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5560,7 +5560,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>11871</t>
+          <t>11125</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>30556</t>
+          <t>29098</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>26860</t>
+          <t>26496</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>53870</t>
+          <t>50891</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>7,67%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>228793</t>
+          <t>230019</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>243440</t>
+          <t>243683</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>92,06%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>370611</t>
+          <t>369698</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>384354</t>
+          <t>383545</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>604784</t>
+          <t>604674</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>624461</t>
+          <t>624830</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,81%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>6411</t>
+          <t>6168</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>21058</t>
+          <t>19832</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>4625</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>18368</t>
+          <t>19281</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>14369</t>
+          <t>14000</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>34046</t>
+          <t>34156</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,35%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1850019</t>
+          <t>1844031</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1965044</t>
+          <t>1970458</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>53,99%</t>
+          <t>53,81%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>57,34%</t>
+          <t>57,5%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2409124</t>
+          <t>2401120</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2519358</t>
+          <t>2517117</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>67,7%</t>
+          <t>67,48%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>70,8%</t>
+          <t>70,74%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4292739</t>
+          <t>4284597</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4457638</t>
+          <t>4451431</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>61,46%</t>
+          <t>61,34%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>63,82%</t>
+          <t>63,73%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1461735</t>
+          <t>1456321</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1576760</t>
+          <t>1582748</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>42,66%</t>
+          <t>42,5%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>46,01%</t>
+          <t>46,19%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1038951</t>
+          <t>1041192</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1149185</t>
+          <t>1157189</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>29,26%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>32,3%</t>
+          <t>32,52%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2527450</t>
+          <t>2533657</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2692349</t>
+          <t>2700491</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>36,18%</t>
+          <t>36,27%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>38,66%</t>
         </is>
       </c>
     </row>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>118665</t>
+          <t>116517</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>159125</t>
+          <t>158268</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>27,78%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>37,94%</t>
+          <t>37,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>127239</t>
+          <t>127509</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>164726</t>
+          <t>163832</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>32,22%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>41,62%</t>
+          <t>41,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>255241</t>
+          <t>254837</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>309145</t>
+          <t>310636</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>31,31%</t>
+          <t>31,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>37,92%</t>
+          <t>38,1%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>260338</t>
+          <t>261195</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>300798</t>
+          <t>302946</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>62,06%</t>
+          <t>62,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>71,71%</t>
+          <t>72,22%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>231029</t>
+          <t>231923</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>268516</t>
+          <t>268246</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>58,38%</t>
+          <t>58,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>67,85%</t>
+          <t>67,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>506073</t>
+          <t>504582</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>559977</t>
+          <t>560381</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>62,08%</t>
+          <t>61,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>68,69%</t>
+          <t>68,74%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>155028</t>
+          <t>157868</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>201115</t>
+          <t>201504</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,06%</t>
+          <t>34,12%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>214339</t>
+          <t>213927</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>261046</t>
+          <t>258707</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>38,03%</t>
+          <t>37,96%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>46,32%</t>
+          <t>45,91%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>379943</t>
+          <t>385223</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>445076</t>
+          <t>447573</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>32,92%</t>
+          <t>33,38%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>38,57%</t>
+          <t>38,78%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>389381</t>
+          <t>388992</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>435468</t>
+          <t>432628</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>65,94%</t>
+          <t>65,88%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>73,75%</t>
+          <t>73,27%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>302498</t>
+          <t>304837</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>349205</t>
+          <t>349617</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>53,68%</t>
+          <t>54,09%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>61,97%</t>
+          <t>62,04%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>708964</t>
+          <t>706467</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>774097</t>
+          <t>768817</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>61,43%</t>
+          <t>61,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>67,08%</t>
+          <t>66,62%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>220995</t>
+          <t>218969</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>270743</t>
+          <t>273375</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>33,03%</t>
+          <t>32,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>40,46%</t>
+          <t>40,86%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>308319</t>
+          <t>307756</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>358037</t>
+          <t>356988</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>46,62%</t>
+          <t>46,53%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>54,13%</t>
+          <t>53,98%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>538570</t>
+          <t>541306</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>613279</t>
+          <t>613733</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>40,48%</t>
+          <t>40,68%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>46,09%</t>
+          <t>46,13%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>398354</t>
+          <t>395722</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>448102</t>
+          <t>450128</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>59,54%</t>
+          <t>59,14%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>66,97%</t>
+          <t>67,27%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>303349</t>
+          <t>304398</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>353067</t>
+          <t>353630</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>45,87%</t>
+          <t>46,02%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>53,38%</t>
+          <t>53,47%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>717204</t>
+          <t>716750</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>791913</t>
+          <t>789177</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>53,91%</t>
+          <t>53,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>59,52%</t>
+          <t>59,32%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>328173</t>
+          <t>328265</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>382048</t>
+          <t>380984</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>50,8%</t>
+          <t>50,81%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>59,14%</t>
+          <t>58,97%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>376058</t>
+          <t>374933</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>427592</t>
+          <t>424929</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>57,94%</t>
+          <t>57,76%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>65,88%</t>
+          <t>65,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>720727</t>
+          <t>721937</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>792782</t>
+          <t>793037</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>55,65%</t>
+          <t>55,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>61,21%</t>
+          <t>61,23%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>264000</t>
+          <t>265064</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>317875</t>
+          <t>317783</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>40,86%</t>
+          <t>41,03%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>49,2%</t>
+          <t>49,19%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>221485</t>
+          <t>224148</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>273019</t>
+          <t>274144</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>34,12%</t>
+          <t>34,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>42,06%</t>
+          <t>42,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>502343</t>
+          <t>502088</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>574398</t>
+          <t>573188</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>38,79%</t>
+          <t>38,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>44,35%</t>
+          <t>44,26%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>296152</t>
+          <t>298546</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>341565</t>
+          <t>339853</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>61,97%</t>
+          <t>62,47%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>71,47%</t>
+          <t>71,11%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>392598</t>
+          <t>390278</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>428656</t>
+          <t>428819</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>79,02%</t>
+          <t>78,55%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>86,27%</t>
+          <t>86,31%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>702578</t>
+          <t>701422</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>761040</t>
+          <t>756727</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>72,08%</t>
+          <t>71,96%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>78,07%</t>
+          <t>77,63%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>136353</t>
+          <t>138065</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>181766</t>
+          <t>179372</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>28,89%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>38,03%</t>
+          <t>37,53%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>68193</t>
+          <t>68030</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>104251</t>
+          <t>106571</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>213727</t>
+          <t>218040</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>272189</t>
+          <t>273345</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>28,04%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>283739</t>
+          <t>283694</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>307424</t>
+          <t>306888</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>84,87%</t>
+          <t>84,85%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>91,95%</t>
+          <t>91,79%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>332340</t>
+          <t>332515</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>354968</t>
+          <t>355139</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>87,98%</t>
+          <t>88,02%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>624066</t>
+          <t>623606</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>657327</t>
+          <t>657134</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>87,64%</t>
+          <t>87,57%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>92,28%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>26906</t>
+          <t>27442</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>50591</t>
+          <t>50636</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>22794</t>
+          <t>22623</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>45422</t>
+          <t>45247</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>54765</t>
+          <t>54958</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>88026</t>
+          <t>88486</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,43%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>232261</t>
+          <t>232867</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>246847</t>
+          <t>246517</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>90,61%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>377794</t>
+          <t>375921</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>393809</t>
+          <t>393709</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>93,94%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>615331</t>
+          <t>615843</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>637126</t>
+          <t>637071</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,94%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>10151</t>
+          <t>10481</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>24737</t>
+          <t>24131</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>6360</t>
+          <t>6460</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>22375</t>
+          <t>24248</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>20041</t>
+          <t>20096</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>41836</t>
+          <t>41324</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,29%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1714718</t>
+          <t>1708608</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1829476</t>
+          <t>1830690</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>50,52%</t>
+          <t>50,34%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>53,9%</t>
+          <t>53,93%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2204921</t>
+          <t>2200429</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2318325</t>
+          <t>2313834</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>62,21%</t>
+          <t>62,08%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>65,41%</t>
+          <t>65,28%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3954961</t>
+          <t>3947609</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4114052</t>
+          <t>4111313</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>57,0%</t>
+          <t>56,89%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>59,29%</t>
+          <t>59,25%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1564874</t>
+          <t>1563660</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1679632</t>
+          <t>1685742</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>46,1%</t>
+          <t>46,07%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>49,48%</t>
+          <t>49,66%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1226217</t>
+          <t>1230708</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1339621</t>
+          <t>1344113</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>34,59%</t>
+          <t>34,72%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>37,79%</t>
+          <t>37,92%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2824840</t>
+          <t>2827579</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2983931</t>
+          <t>2991283</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>40,71%</t>
+          <t>40,75%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>43,0%</t>
+          <t>43,11%</t>
         </is>
       </c>
     </row>
@@ -9665,32 +9665,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>114838</t>
+          <t>96843</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>84062</t>
+          <t>70982</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>149159</t>
+          <t>124844</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>37,29%</t>
+          <t>30,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9700,32 +9700,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>87970</t>
+          <t>102244</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>66973</t>
+          <t>78855</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>111138</t>
+          <t>126144</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>35,48%</t>
+          <t>34,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9735,32 +9735,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>202808</t>
+          <t>199087</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>165126</t>
+          <t>166553</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>244639</t>
+          <t>239491</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>31,09%</t>
         </is>
       </c>
     </row>
@@ -9778,32 +9778,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>285149</t>
+          <t>310950</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>250828</t>
+          <t>282949</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>315925</t>
+          <t>336811</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>71,29%</t>
+          <t>76,25%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>62,71%</t>
+          <t>69,39%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>78,98%</t>
+          <t>82,59%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9813,32 +9813,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>225230</t>
+          <t>260268</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>202062</t>
+          <t>236368</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>246227</t>
+          <t>283657</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>71,91%</t>
+          <t>71,8%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>64,52%</t>
+          <t>65,2%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>78,62%</t>
+          <t>78,25%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9848,32 +9848,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>510379</t>
+          <t>571218</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>468548</t>
+          <t>530814</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>548061</t>
+          <t>603752</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>71,56%</t>
+          <t>74,15%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>65,7%</t>
+          <t>68,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>76,85%</t>
+          <t>78,38%</t>
         </is>
       </c>
     </row>
@@ -9891,17 +9891,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9926,17 +9926,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9961,17 +9961,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10008,32 +10008,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>121227</t>
+          <t>128500</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>99239</t>
+          <t>105699</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>146118</t>
+          <t>155263</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>26,95%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>32,56%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10043,32 +10043,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>124331</t>
+          <t>133062</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>79495</t>
+          <t>113125</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>155836</t>
+          <t>155381</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>30,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10078,32 +10078,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>245558</t>
+          <t>261562</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>188016</t>
+          <t>229753</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>284718</t>
+          <t>295511</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>30,2%</t>
         </is>
       </c>
     </row>
@@ -10121,32 +10121,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>302320</t>
+          <t>348390</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>277429</t>
+          <t>321627</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>324308</t>
+          <t>371191</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>71,38%</t>
+          <t>73,05%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>65,5%</t>
+          <t>67,44%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>76,57%</t>
+          <t>77,84%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10156,32 +10156,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>387762</t>
+          <t>368671</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>356257</t>
+          <t>346352</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>432598</t>
+          <t>388608</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>75,72%</t>
+          <t>73,48%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>69,57%</t>
+          <t>69,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,48%</t>
+          <t>77,45%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10191,32 +10191,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>690082</t>
+          <t>717061</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>650922</t>
+          <t>683112</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>747624</t>
+          <t>748870</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>73,76%</t>
+          <t>73,27%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>69,57%</t>
+          <t>69,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>79,91%</t>
+          <t>76,52%</t>
         </is>
       </c>
     </row>
@@ -10234,17 +10234,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10269,17 +10269,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10304,17 +10304,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10351,32 +10351,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>133721</t>
+          <t>150445</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>116543</t>
+          <t>127945</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>157272</t>
+          <t>172977</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>27,86%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10386,32 +10386,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>173986</t>
+          <t>197136</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>129923</t>
+          <t>177719</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>199968</t>
+          <t>216575</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>31,63%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>28,52%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>34,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10421,32 +10421,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>307707</t>
+          <t>347581</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>261730</t>
+          <t>317837</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>338470</t>
+          <t>376627</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>27,94%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>30,27%</t>
         </is>
       </c>
     </row>
@@ -10464,32 +10464,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>402617</t>
+          <t>470392</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>379066</t>
+          <t>447860</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>419795</t>
+          <t>492892</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>75,07%</t>
+          <t>75,77%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>70,68%</t>
+          <t>72,14%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>78,27%</t>
+          <t>79,39%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10499,32 +10499,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>418016</t>
+          <t>426057</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>392034</t>
+          <t>406618</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>462079</t>
+          <t>445474</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>70,61%</t>
+          <t>68,37%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>66,22%</t>
+          <t>65,25%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>78,05%</t>
+          <t>71,48%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10534,32 +10534,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>820633</t>
+          <t>896448</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>789870</t>
+          <t>867402</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>866610</t>
+          <t>926192</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>72,73%</t>
+          <t>72,06%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>70,0%</t>
+          <t>69,73%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>76,8%</t>
+          <t>74,45%</t>
         </is>
       </c>
     </row>
@@ -10577,17 +10577,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10612,17 +10612,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>592002</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>592002</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>592002</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1128340</t>
+          <t>1244029</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1128340</t>
+          <t>1244029</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1128340</t>
+          <t>1244029</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10694,32 +10694,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>248815</t>
+          <t>268258</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>108373</t>
+          <t>242120</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>354972</t>
+          <t>297481</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>38,29%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>34,56%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>39,98%</t>
+          <t>42,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10729,32 +10729,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>296830</t>
+          <t>318176</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>247699</t>
+          <t>296197</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>322565</t>
+          <t>338169</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>41,64%</t>
+          <t>43,18%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>34,75%</t>
+          <t>40,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>45,25%</t>
+          <t>45,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10764,32 +10764,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>545645</t>
+          <t>586435</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>348805</t>
+          <t>553264</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>662693</t>
+          <t>619590</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>34,09%</t>
+          <t>40,8%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>38,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>41,4%</t>
+          <t>43,1%</t>
         </is>
       </c>
     </row>
@@ -10807,32 +10807,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>638971</t>
+          <t>432359</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>532814</t>
+          <t>403136</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>779413</t>
+          <t>458497</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>71,97%</t>
+          <t>61,71%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>60,02%</t>
+          <t>57,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,79%</t>
+          <t>65,44%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10842,32 +10842,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>416051</t>
+          <t>418710</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>390316</t>
+          <t>398717</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>465182</t>
+          <t>440689</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>58,36%</t>
+          <t>56,82%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>54,75%</t>
+          <t>54,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>65,25%</t>
+          <t>59,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10877,32 +10877,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1055022</t>
+          <t>851069</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>937974</t>
+          <t>817914</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1251862</t>
+          <t>884240</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>65,91%</t>
+          <t>59,2%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>58,6%</t>
+          <t>56,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,21%</t>
+          <t>61,51%</t>
         </is>
       </c>
     </row>
@@ -10920,17 +10920,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10955,17 +10955,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10990,17 +10990,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11037,32 +11037,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>296422</t>
+          <t>313355</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>274241</t>
+          <t>289346</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>319166</t>
+          <t>338486</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>52,82%</t>
+          <t>51,42%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>48,86%</t>
+          <t>47,48%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>56,87%</t>
+          <t>55,55%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11072,32 +11072,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>301097</t>
+          <t>336355</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>283458</t>
+          <t>317972</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>319988</t>
+          <t>355535</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>54,95%</t>
+          <t>55,24%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>51,73%</t>
+          <t>52,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>58,4%</t>
+          <t>58,39%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11107,32 +11107,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>597519</t>
+          <t>649711</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>570430</t>
+          <t>622103</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>625548</t>
+          <t>681852</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>53,87%</t>
+          <t>53,33%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>51,43%</t>
+          <t>51,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>56,4%</t>
+          <t>55,97%</t>
         </is>
       </c>
     </row>
@@ -11150,32 +11150,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>264812</t>
+          <t>295991</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>242068</t>
+          <t>270860</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>286993</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>47,18%</t>
+          <t>48,58%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>43,13%</t>
+          <t>44,45%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>51,14%</t>
+          <t>52,52%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11185,32 +11185,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>246808</t>
+          <t>272500</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>227917</t>
+          <t>253320</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>264447</t>
+          <t>290883</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>45,05%</t>
+          <t>44,76%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>41,6%</t>
+          <t>41,61%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>48,27%</t>
+          <t>47,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11220,32 +11220,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>511620</t>
+          <t>568491</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>483591</t>
+          <t>536350</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>538709</t>
+          <t>596099</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>46,13%</t>
+          <t>46,67%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>43,6%</t>
+          <t>44,03%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>48,57%</t>
+          <t>48,93%</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11298,17 +11298,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11333,17 +11333,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11380,32 +11380,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>200003</t>
+          <t>218401</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>185915</t>
+          <t>201679</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>216279</t>
+          <t>235158</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>54,32%</t>
+          <t>53,65%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>50,5%</t>
+          <t>49,54%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>58,75%</t>
+          <t>57,77%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11415,32 +11415,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>469225</t>
+          <t>288804</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>392704</t>
+          <t>273946</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>545258</t>
+          <t>302134</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>77,13%</t>
+          <t>65,76%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>64,55%</t>
+          <t>62,38%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>68,8%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11450,32 +11450,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>669228</t>
+          <t>507205</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>579561</t>
+          <t>483420</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>815314</t>
+          <t>530906</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>68,53%</t>
+          <t>59,94%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>59,35%</t>
+          <t>57,13%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>83,49%</t>
+          <t>62,74%</t>
         </is>
       </c>
     </row>
@@ -11493,32 +11493,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>168162</t>
+          <t>188679</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>151886</t>
+          <t>171922</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>182250</t>
+          <t>205401</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>45,68%</t>
+          <t>46,35%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>41,25%</t>
+          <t>42,23%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>49,5%</t>
+          <t>50,46%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11528,32 +11528,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>139143</t>
+          <t>150362</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>63110</t>
+          <t>137032</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>215664</t>
+          <t>165220</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>34,24%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>31,2%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>37,62%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11563,32 +11563,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>307305</t>
+          <t>339041</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>161219</t>
+          <t>315340</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>396972</t>
+          <t>362826</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>31,47%</t>
+          <t>40,06%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>37,26%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>40,65%</t>
+          <t>42,87%</t>
         </is>
       </c>
     </row>
@@ -11606,17 +11606,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11641,17 +11641,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>203749</t>
+          <t>222178</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>191394</t>
+          <t>208718</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>214947</t>
+          <t>235853</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>72,06%</t>
+          <t>71,62%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>67,69%</t>
+          <t>67,29%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>76,02%</t>
+          <t>76,03%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11758,32 +11758,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>325379</t>
+          <t>353012</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>312495</t>
+          <t>340023</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>337242</t>
+          <t>366548</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>76,41%</t>
+          <t>75,98%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>73,38%</t>
+          <t>73,18%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>79,2%</t>
+          <t>78,89%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11793,32 +11793,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>529127</t>
+          <t>575190</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>511715</t>
+          <t>557610</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>545290</t>
+          <t>594579</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>74,67%</t>
+          <t>74,24%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>72,22%</t>
+          <t>71,97%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>76,95%</t>
+          <t>76,74%</t>
         </is>
       </c>
     </row>
@@ -11836,32 +11836,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>79010</t>
+          <t>88020</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>67812</t>
+          <t>74345</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>91365</t>
+          <t>101480</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>28,38%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>23,97%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>32,31%</t>
+          <t>32,71%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11871,32 +11871,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>100452</t>
+          <t>111597</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>88589</t>
+          <t>98061</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>113336</t>
+          <t>124586</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>26,82%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11906,32 +11906,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>179463</t>
+          <t>199617</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>163300</t>
+          <t>180228</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>196875</t>
+          <t>217197</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>25,76%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>28,03%</t>
         </is>
       </c>
     </row>
@@ -11949,17 +11949,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11984,17 +11984,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12019,17 +12019,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1318774</t>
+          <t>1397982</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1022275</t>
+          <t>1339425</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1443659</t>
+          <t>1464117</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>38,12%</t>
+          <t>39,57%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>37,91%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>41,73%</t>
+          <t>41,44%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>1778817</t>
+          <t>1728788</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1633608</t>
+          <t>1679038</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2158123</t>
+          <t>1785648</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>47,92%</t>
+          <t>46,26%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>44,01%</t>
+          <t>44,93%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>58,13%</t>
+          <t>47,78%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12136,32 +12136,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>3097592</t>
+          <t>3126771</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2822782</t>
+          <t>3042214</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3424282</t>
+          <t>3215997</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>43,19%</t>
+          <t>43,01%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>39,36%</t>
+          <t>41,85%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>47,74%</t>
+          <t>44,24%</t>
         </is>
       </c>
     </row>
@@ -12179,32 +12179,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>2141043</t>
+          <t>2134780</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2016158</t>
+          <t>2068645</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2437542</t>
+          <t>2193337</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>61,88%</t>
+          <t>60,43%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>58,27%</t>
+          <t>58,56%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>70,45%</t>
+          <t>62,09%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>1933463</t>
+          <t>2008166</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1554157</t>
+          <t>1951306</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2078672</t>
+          <t>2057916</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>52,08%</t>
+          <t>53,74%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>41,87%</t>
+          <t>52,22%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>55,99%</t>
+          <t>55,07%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12249,32 +12249,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>4074505</t>
+          <t>4142945</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3747815</t>
+          <t>4053719</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4349315</t>
+          <t>4227502</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>56,81%</t>
+          <t>56,99%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>52,26%</t>
+          <t>55,76%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>60,64%</t>
+          <t>58,15%</t>
         </is>
       </c>
     </row>
@@ -12292,17 +12292,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12362,17 +12362,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">

--- a/data/trans_orig/P2A_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P2A_R-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con alguna condición, enfermedad crónica o limitación en 2007 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con alguna condición, enfermedad crónica o limitación en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con alguna condición, enfermedad crónica o limitación en 2012 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con alguna condición, enfermedad crónica o limitación en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con alguna condición, enfermedad crónica o limitación en 2016 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con alguna condición, enfermedad crónica o limitación en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con alguna condición, enfermedad crónica o limitación en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con alguna condición, enfermedad crónica o limitación en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
